--- a/codice/concentrazioni_polliniche.xlsx
+++ b/codice/concentrazioni_polliniche.xlsx
@@ -202,7 +202,7 @@
     <t xml:space="preserve">Alternaria</t>
   </si>
   <si>
-    <t xml:space="preserve">0 – 1</t>
+    <t xml:space="preserve">0 – 1,9</t>
   </si>
   <si>
     <t xml:space="preserve">2 – 19</t>
@@ -387,32 +387,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -671,491 +675,491 @@
   <dimension ref="A1:E101"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>82</v>
       </c>
     </row>
